--- a/OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
+++ b/OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.1764</v>
+        <v>0.1765293882447021</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.1246</v>
+        <v>0.124750099960016</v>
       </c>
     </row>
   </sheetData>
